--- a/data/trans_orig/P6713-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6713-Estudios-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le permite que aprenda cosas nuevas en 2012</t>
+          <t>Población según si su trabajo le permite que aprenda cosas nuevas en 2012 (tasa de respuesta: 99,1%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6391</t>
+          <t>6091</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21711</t>
+          <t>21427</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6939</t>
+          <t>7146</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22440</t>
+          <t>22021</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16797</t>
+          <t>16604</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38543</t>
+          <t>38036</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,78%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5547</t>
+          <t>5459</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18718</t>
+          <t>18927</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4167</t>
+          <t>4417</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16262</t>
+          <t>16745</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11480</t>
+          <t>12350</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29584</t>
+          <t>30658</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,49%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22928</t>
+          <t>23803</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>45595</t>
+          <t>46483</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27623</t>
+          <t>27193</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>48297</t>
+          <t>48608</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>56101</t>
+          <t>54639</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>87436</t>
+          <t>85843</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>26,58%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28614</t>
+          <t>28599</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52319</t>
+          <t>51613</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8355</t>
+          <t>8021</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23369</t>
+          <t>23088</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42264</t>
+          <t>42178</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70025</t>
+          <t>69252</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,44%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>73178</t>
+          <t>73331</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>101052</t>
+          <t>101381</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53670</t>
+          <t>53682</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>78469</t>
+          <t>79055</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>136524</t>
+          <t>135386</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>172479</t>
+          <t>171525</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>53,11%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30147</t>
+          <t>30823</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57895</t>
+          <t>57614</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30475</t>
+          <t>30420</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56677</t>
+          <t>57569</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66930</t>
+          <t>65502</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>103013</t>
+          <t>102008</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36042</t>
+          <t>37412</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>66111</t>
+          <t>65789</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32828</t>
+          <t>31678</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>61973</t>
+          <t>58746</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>76053</t>
+          <t>74766</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>116800</t>
+          <t>117829</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>178283</t>
+          <t>178191</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>229506</t>
+          <t>228032</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>112918</t>
+          <t>113561</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>154996</t>
+          <t>155745</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>304081</t>
+          <t>302363</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>371288</t>
+          <t>367195</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,8%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>193836</t>
+          <t>196066</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>245757</t>
+          <t>247373</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,49 +1767,49 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>27,11%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>134488</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>113100</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>153133</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>23,66%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>19,9%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
           <t>26,94%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>134488</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>113656</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>155647</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>23,66%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>19,99%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>27,38%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>337</t>
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>321813</t>
+          <t>319426</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>388517</t>
+          <t>386514</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,1%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>365351</t>
+          <t>368309</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>428950</t>
+          <t>429604</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>189454</t>
+          <t>191457</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>236694</t>
+          <t>238231</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>572105</t>
+          <t>574354</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>654198</t>
+          <t>652578</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>44,07%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>883</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13141</t>
+          <t>12302</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1978</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11218</t>
+          <t>12016</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>4388</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18430</t>
+          <t>20022</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7780</t>
+          <t>8547</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26490</t>
+          <t>27134</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5175</t>
+          <t>5152</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19540</t>
+          <t>19121</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15487</t>
+          <t>15959</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>38036</t>
+          <t>39520</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>38732</t>
+          <t>38094</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>65698</t>
+          <t>66668</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>19155</t>
+          <t>18318</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40613</t>
+          <t>40065</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>63191</t>
+          <t>62388</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>97799</t>
+          <t>96965</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,63%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51976</t>
+          <t>52606</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>83161</t>
+          <t>82225</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35114</t>
+          <t>36585</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>61981</t>
+          <t>63975</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>94768</t>
+          <t>95175</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>133684</t>
+          <t>137188</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,94%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>160479</t>
+          <t>160723</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>197250</t>
+          <t>198408</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>126756</t>
+          <t>124503</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>158248</t>
+          <t>157292</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>53,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>297850</t>
+          <t>298654</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>348851</t>
+          <t>346656</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>63,02%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>43311</t>
+          <t>44799</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>76740</t>
+          <t>75031</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>47299</t>
+          <t>47136</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>77381</t>
+          <t>77596</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>99581</t>
+          <t>96903</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>147276</t>
+          <t>142234</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>59330</t>
+          <t>59862</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>95088</t>
+          <t>96379</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>49061</t>
+          <t>48061</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>82047</t>
+          <t>80845</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>117405</t>
+          <t>117797</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>166065</t>
+          <t>165449</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>254512</t>
+          <t>255861</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>316164</t>
+          <t>318124</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>173529</t>
+          <t>172870</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>226562</t>
+          <t>224768</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>448902</t>
+          <t>444042</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>527744</t>
+          <t>528355</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,45%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>292575</t>
+          <t>291620</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>356572</t>
+          <t>355859</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>171314</t>
+          <t>172183</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>225164</t>
+          <t>225105</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>478940</t>
+          <t>480915</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>561168</t>
+          <t>563913</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,96%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>630170</t>
+          <t>627021</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>707023</t>
+          <t>704527</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>391912</t>
+          <t>390623</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>456274</t>
+          <t>455553</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1041947</t>
+          <t>1039058</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1136929</t>
+          <t>1143126</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>48,56%</t>
         </is>
       </c>
     </row>
@@ -3495,7 +3495,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le permite que aprenda cosas nuevas en 2016</t>
+          <t>Población según si su trabajo le permite que aprenda cosas nuevas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7463</t>
+          <t>6261</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22602</t>
+          <t>20798</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4040</t>
+          <t>4038</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15007</t>
+          <t>14598</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13452</t>
+          <t>12806</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31425</t>
+          <t>32563</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>15,13%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14688</t>
+          <t>15185</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32639</t>
+          <t>33176</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10212</t>
+          <t>10708</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24248</t>
+          <t>24569</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28921</t>
+          <t>28567</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53249</t>
+          <t>52974</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,62%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31447</t>
+          <t>31697</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53208</t>
+          <t>54450</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12659</t>
+          <t>11649</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28480</t>
+          <t>26241</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>47725</t>
+          <t>48366</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>75076</t>
+          <t>74515</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,63%</t>
         </is>
       </c>
     </row>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21585</t>
+          <t>22877</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42442</t>
+          <t>42719</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9101</t>
+          <t>9382</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22996</t>
+          <t>23105</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34817</t>
+          <t>35059</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59192</t>
+          <t>60018</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,89%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24162</t>
+          <t>24504</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>45059</t>
+          <t>45226</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7336</t>
+          <t>8089</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>20418</t>
+          <t>22358</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>34875</t>
+          <t>35679</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>61171</t>
+          <t>59136</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>27,48%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>49301</t>
+          <t>49056</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>81655</t>
+          <t>80593</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>56844</t>
+          <t>56590</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>88607</t>
+          <t>86560</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>114338</t>
+          <t>113379</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>157397</t>
+          <t>158230</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80615</t>
+          <t>79479</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>118626</t>
+          <t>116278</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>76433</t>
+          <t>76671</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>110502</t>
+          <t>109631</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>163878</t>
+          <t>165927</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>215117</t>
+          <t>214067</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,57%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>214046</t>
+          <t>215406</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>272052</t>
+          <t>269071</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>133223</t>
+          <t>130694</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>175627</t>
+          <t>173591</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>359404</t>
+          <t>359596</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>432286</t>
+          <t>430943</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,31%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>230689</t>
+          <t>232265</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>283693</t>
+          <t>288500</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>162364</t>
+          <t>165947</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>211314</t>
+          <t>211547</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>411226</t>
+          <t>408489</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>483332</t>
+          <t>481925</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,54%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>237748</t>
+          <t>238025</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>294994</t>
+          <t>297119</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>129265</t>
+          <t>130357</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>174628</t>
+          <t>172665</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>382514</t>
+          <t>380839</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>456087</t>
+          <t>450211</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,53%</t>
         </is>
       </c>
     </row>
@@ -5054,12 +5054,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1876</t>
+          <t>1791</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12347</t>
+          <t>10713</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5389</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20123</t>
+          <t>21405</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8732</t>
+          <t>9200</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26717</t>
+          <t>27827</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10764</t>
+          <t>11182</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28600</t>
+          <t>28934</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5182,12 +5182,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5202,12 +5202,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12776</t>
+          <t>11973</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28258</t>
+          <t>28784</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5237,12 +5237,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26725</t>
+          <t>26413</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>50622</t>
+          <t>51697</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -5280,12 +5280,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>56927</t>
+          <t>56658</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>89577</t>
+          <t>88645</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5295,12 +5295,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5315,12 +5315,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>44840</t>
+          <t>44330</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>72473</t>
+          <t>69973</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5350,12 +5350,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>108679</t>
+          <t>109888</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>149835</t>
+          <t>149798</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5365,7 +5365,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>59669</t>
+          <t>59752</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>91560</t>
+          <t>92050</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5408,12 +5408,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5428,12 +5428,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>56907</t>
+          <t>57966</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>86601</t>
+          <t>86943</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>126516</t>
+          <t>124513</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>168530</t>
+          <t>169577</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,73%</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>161285</t>
+          <t>160664</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>200379</t>
+          <t>200490</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>133380</t>
+          <t>132674</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>167072</t>
+          <t>167174</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>303869</t>
+          <t>302012</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>353924</t>
+          <t>354784</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>53,83%</t>
         </is>
       </c>
     </row>
@@ -5736,12 +5736,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>66354</t>
+          <t>65080</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>103224</t>
+          <t>101281</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5751,12 +5751,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>72246</t>
+          <t>74477</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>108294</t>
+          <t>111576</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>147615</t>
+          <t>147804</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>197461</t>
+          <t>199097</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -5849,12 +5849,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>116220</t>
+          <t>116255</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>160567</t>
+          <t>163487</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>108100</t>
+          <t>107023</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>150092</t>
+          <t>150001</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>235773</t>
+          <t>235347</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>296003</t>
+          <t>295732</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,06%</t>
         </is>
       </c>
     </row>
@@ -5962,12 +5962,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>323017</t>
+          <t>323585</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>390330</t>
+          <t>390237</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5977,12 +5977,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>203444</t>
+          <t>200194</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>255025</t>
+          <t>255330</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6012,12 +6012,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>544507</t>
+          <t>543375</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>629297</t>
+          <t>628342</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6047,12 +6047,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,62%</t>
         </is>
       </c>
     </row>
@@ -6075,12 +6075,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>331665</t>
+          <t>332174</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>396880</t>
+          <t>397861</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6090,12 +6090,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>246476</t>
+          <t>248605</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>304380</t>
+          <t>303902</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6125,12 +6125,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>595259</t>
+          <t>599190</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>683110</t>
+          <t>681904</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6160,12 +6160,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,81%</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>443897</t>
+          <t>444235</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>519592</t>
+          <t>517134</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>285201</t>
+          <t>283224</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>346485</t>
+          <t>341505</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>745028</t>
+          <t>746947</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>840865</t>
+          <t>840140</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,26%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6713-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6713-Estudios-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6091</t>
+          <t>6166</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21427</t>
+          <t>21041</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7146</t>
+          <t>6814</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22021</t>
+          <t>21331</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16604</t>
+          <t>17036</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38036</t>
+          <t>37222</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,53%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5459</t>
+          <t>5827</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18927</t>
+          <t>19583</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4417</t>
+          <t>3410</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16745</t>
+          <t>16839</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12350</t>
+          <t>12710</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30658</t>
+          <t>30162</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,34%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23803</t>
+          <t>23335</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>46483</t>
+          <t>44659</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27193</t>
+          <t>26748</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>48608</t>
+          <t>48650</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>54639</t>
+          <t>55168</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>85843</t>
+          <t>86830</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,89%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28599</t>
+          <t>28908</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51613</t>
+          <t>52459</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8021</t>
+          <t>7788</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23088</t>
+          <t>22647</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42178</t>
+          <t>41581</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>69252</t>
+          <t>68217</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,12%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>73331</t>
+          <t>73645</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>101381</t>
+          <t>100543</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53682</t>
+          <t>54934</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>79055</t>
+          <t>79016</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>135386</t>
+          <t>135552</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>171525</t>
+          <t>172464</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>53,4%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30823</t>
+          <t>30442</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57614</t>
+          <t>57311</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30420</t>
+          <t>31142</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57569</t>
+          <t>56568</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65502</t>
+          <t>68037</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>102008</t>
+          <t>103567</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37412</t>
+          <t>35302</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>65789</t>
+          <t>65507</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31678</t>
+          <t>32063</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>58746</t>
+          <t>57992</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>74766</t>
+          <t>75184</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>117829</t>
+          <t>114211</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>178191</t>
+          <t>176832</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>228032</t>
+          <t>230638</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>113561</t>
+          <t>114736</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>155745</t>
+          <t>157130</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>302363</t>
+          <t>304906</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>367195</t>
+          <t>370926</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>25,05%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>196066</t>
+          <t>192038</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>247373</t>
+          <t>247603</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>113100</t>
+          <t>113854</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>153133</t>
+          <t>155573</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>319426</t>
+          <t>320356</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>386514</t>
+          <t>386290</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,09%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>368309</t>
+          <t>368639</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>429604</t>
+          <t>426293</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>191457</t>
+          <t>191582</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>238231</t>
+          <t>238059</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>574354</t>
+          <t>573882</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>652578</t>
+          <t>652869</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>44,09%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>883</t>
+          <t>901</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12302</t>
+          <t>12883</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12016</t>
+          <t>12062</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4388</t>
+          <t>4227</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20022</t>
+          <t>18373</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8547</t>
+          <t>7627</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27134</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>4974</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19121</t>
+          <t>19481</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15959</t>
+          <t>15984</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39520</t>
+          <t>39232</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>38094</t>
+          <t>37357</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>66668</t>
+          <t>65921</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>18318</t>
+          <t>18196</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40065</t>
+          <t>40765</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>62388</t>
+          <t>62723</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>96965</t>
+          <t>98934</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,98%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52606</t>
+          <t>50264</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>82225</t>
+          <t>82120</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36585</t>
+          <t>36199</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>63975</t>
+          <t>63527</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>95175</t>
+          <t>94939</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>137188</t>
+          <t>135844</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,69%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>160723</t>
+          <t>161187</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>198408</t>
+          <t>199957</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>51,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>124503</t>
+          <t>126124</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>157292</t>
+          <t>159492</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>298654</t>
+          <t>294985</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>346656</t>
+          <t>345903</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,02%</t>
+          <t>62,88%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>44799</t>
+          <t>45629</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>75031</t>
+          <t>76295</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>47136</t>
+          <t>45786</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>77596</t>
+          <t>77180</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>96903</t>
+          <t>98812</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>142234</t>
+          <t>143424</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>59862</t>
+          <t>59088</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>96379</t>
+          <t>96039</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>48061</t>
+          <t>48784</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>80845</t>
+          <t>82440</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>117797</t>
+          <t>117486</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>165449</t>
+          <t>166409</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>255861</t>
+          <t>254792</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>318124</t>
+          <t>321917</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>172870</t>
+          <t>175967</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>224768</t>
+          <t>226927</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>444042</t>
+          <t>444614</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>528355</t>
+          <t>524529</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,28%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>291620</t>
+          <t>290495</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>355859</t>
+          <t>354695</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>172183</t>
+          <t>174070</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>225105</t>
+          <t>226405</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>480915</t>
+          <t>481270</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>563913</t>
+          <t>565940</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,04%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>627021</t>
+          <t>628775</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>704527</t>
+          <t>705519</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>390623</t>
+          <t>389369</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>455553</t>
+          <t>451548</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1039058</t>
+          <t>1037606</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1143126</t>
+          <t>1139609</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,41%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6261</t>
+          <t>6756</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20798</t>
+          <t>20301</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4038</t>
+          <t>3993</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14598</t>
+          <t>15182</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12806</t>
+          <t>13605</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32563</t>
+          <t>31237</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>14,51%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15185</t>
+          <t>14822</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33176</t>
+          <t>32986</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10708</t>
+          <t>10603</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24569</t>
+          <t>24565</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28567</t>
+          <t>28928</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52974</t>
+          <t>52497</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,39%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31697</t>
+          <t>31210</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>54450</t>
+          <t>54612</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11649</t>
+          <t>12706</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26241</t>
+          <t>26828</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>48366</t>
+          <t>47435</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>74515</t>
+          <t>74816</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,77%</t>
         </is>
       </c>
     </row>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22877</t>
+          <t>22180</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42719</t>
+          <t>42968</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9382</t>
+          <t>8692</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23105</t>
+          <t>22573</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35059</t>
+          <t>35585</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60018</t>
+          <t>59231</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,52%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24504</t>
+          <t>23148</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>45226</t>
+          <t>45105</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8089</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22358</t>
+          <t>21539</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>35679</t>
+          <t>35439</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>59136</t>
+          <t>60074</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,91%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>49056</t>
+          <t>47848</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80593</t>
+          <t>81892</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>56590</t>
+          <t>55977</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>86560</t>
+          <t>89844</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>113379</t>
+          <t>113903</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>158230</t>
+          <t>158670</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,06%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79479</t>
+          <t>80054</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>116278</t>
+          <t>116134</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>76671</t>
+          <t>74582</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>109631</t>
+          <t>109856</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>165927</t>
+          <t>161934</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>214067</t>
+          <t>214672</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,6%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>215406</t>
+          <t>213196</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>269071</t>
+          <t>267725</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>130694</t>
+          <t>130086</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>173591</t>
+          <t>174634</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>359596</t>
+          <t>360249</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>430943</t>
+          <t>431810</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,36%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>232265</t>
+          <t>230118</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>288500</t>
+          <t>285525</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>165947</t>
+          <t>165908</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>211547</t>
+          <t>211977</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>408489</t>
+          <t>409909</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>481925</t>
+          <t>481785</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,53%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>238025</t>
+          <t>238224</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>297119</t>
+          <t>294952</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>130357</t>
+          <t>127990</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>172665</t>
+          <t>173431</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>380839</t>
+          <t>383605</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>450211</t>
+          <t>459203</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>29,1%</t>
         </is>
       </c>
     </row>
@@ -5054,12 +5054,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>1866</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10713</t>
+          <t>12459</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5389</t>
+          <t>5839</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21405</t>
+          <t>20958</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9200</t>
+          <t>9314</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27827</t>
+          <t>25837</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11182</t>
+          <t>10298</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28934</t>
+          <t>28403</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5182,12 +5182,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5202,12 +5202,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11973</t>
+          <t>11993</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28784</t>
+          <t>28776</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5237,12 +5237,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26413</t>
+          <t>26327</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51697</t>
+          <t>51580</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -5280,12 +5280,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>56658</t>
+          <t>56669</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>88645</t>
+          <t>88016</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5315,12 +5315,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>44330</t>
+          <t>45006</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>69973</t>
+          <t>71656</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5350,12 +5350,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>109888</t>
+          <t>110646</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>149798</t>
+          <t>152753</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>23,18%</t>
         </is>
       </c>
     </row>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>59752</t>
+          <t>58760</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>92050</t>
+          <t>92988</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5408,12 +5408,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5428,12 +5428,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>57966</t>
+          <t>57184</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>86943</t>
+          <t>85400</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>124513</t>
+          <t>125495</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>169577</t>
+          <t>168247</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,53%</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>160664</t>
+          <t>160917</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>200490</t>
+          <t>200345</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>132674</t>
+          <t>131694</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>167174</t>
+          <t>166712</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>302012</t>
+          <t>307097</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>354784</t>
+          <t>356121</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>54,03%</t>
         </is>
       </c>
     </row>
@@ -5736,12 +5736,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>65080</t>
+          <t>64194</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>101281</t>
+          <t>100594</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5751,12 +5751,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>74477</t>
+          <t>73845</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>111576</t>
+          <t>111875</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>147804</t>
+          <t>147776</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>199097</t>
+          <t>199977</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -5849,12 +5849,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>116255</t>
+          <t>116980</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>163487</t>
+          <t>162057</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5864,12 +5864,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>107023</t>
+          <t>109140</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>150001</t>
+          <t>152240</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>235347</t>
+          <t>235233</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>295732</t>
+          <t>297925</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,15%</t>
         </is>
       </c>
     </row>
@@ -5962,12 +5962,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>323585</t>
+          <t>321703</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>390237</t>
+          <t>391408</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5977,12 +5977,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>200194</t>
+          <t>202976</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>255330</t>
+          <t>257262</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6012,12 +6012,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>543375</t>
+          <t>542264</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>628342</t>
+          <t>629472</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6047,12 +6047,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,67%</t>
         </is>
       </c>
     </row>
@@ -6075,12 +6075,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>332174</t>
+          <t>331117</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>397861</t>
+          <t>401378</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6090,12 +6090,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>248605</t>
+          <t>246700</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>303902</t>
+          <t>300733</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6125,12 +6125,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>599190</t>
+          <t>595584</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>681904</t>
+          <t>678791</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6160,12 +6160,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,68%</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>444235</t>
+          <t>444165</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>517134</t>
+          <t>519685</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>283224</t>
+          <t>283696</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>341505</t>
+          <t>343794</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>746947</t>
+          <t>744229</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>840140</t>
+          <t>840481</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,27%</t>
         </is>
       </c>
     </row>
